--- a/plantilla-herramientas.xlsx
+++ b/plantilla-herramientas.xlsx
@@ -447,7 +447,7 @@
         <v>Fixture de ensamble puerta delantera</v>
       </c>
       <c r="C2" t="str">
-        <v>herramienta</v>
+        <v>fixture</v>
       </c>
       <c r="D2" t="str">
         <v>Línea 1</v>
@@ -476,7 +476,7 @@
         <v>Gancho transportador tipo C</v>
       </c>
       <c r="C3" t="str">
-        <v>herramienta</v>
+        <v>gancho</v>
       </c>
       <c r="D3" t="str">
         <v>Línea 2</v>
@@ -499,13 +499,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>MN-3010</v>
+        <v>TL-3010</v>
       </c>
       <c r="B4" t="str">
         <v>Manipulador neumático de panel</v>
       </c>
       <c r="C4" t="str">
-        <v>maquina</v>
+        <v>tooling</v>
       </c>
       <c r="D4" t="str">
         <v>Línea 1</v>
@@ -528,13 +528,13 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>HR-4005</v>
+        <v>TL-4005</v>
       </c>
       <c r="B5" t="str">
         <v>Torquímetro digital calibrado</v>
       </c>
       <c r="C5" t="str">
-        <v>herramienta</v>
+        <v>tooling</v>
       </c>
       <c r="D5" t="str">
         <v>Línea 1</v>
